--- a/test/res/task.xlsx
+++ b/test/res/task.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\bite\Desktop\github\xlsx-exporter\test\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620B5F11-DADE-43CB-B52D-08DC28BEF233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D307FD-8789-4119-8CD7-DAE3100B3F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="660" windowWidth="19185" windowHeight="20070" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31500" yWindow="360" windowWidth="29610" windowHeight="19950" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="9" r:id="rId1"/>
@@ -1100,7 +1100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="260">
   <si>
     <t>id</t>
   </si>
@@ -1884,6 +1884,10 @@
   </si>
   <si>
     <t>@keyvalue</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1]</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -4176,7 +4180,7 @@
         <v>13</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>13</v>
+        <v>259</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>13</v>
